--- a/templates/ja/07_generic_project_30members.xlsx
+++ b/templates/ja/07_generic_project_30members.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ" sheetId="1" r:id="Rd4a272ada09f4af4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R18bbbbb2be884929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ" sheetId="1" r:id="Ra3536483f5f94eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="Rf6ecd2c228da4ebf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,18 +28,12 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="14"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -68,63 +62,19 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -326,993 +276,993 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" s="3" t="str">
         <x:v>名前</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" s="3" t="str">
+        <x:v>フリガナ</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
         <x:v>専門</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="D1" s="3" t="str">
         <x:v>経験</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="E1" s="3" t="str">
         <x:v>コミュニケーション</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="F1" s="3" t="str">
         <x:v>リーダー経験</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="G1" s="3" t="str">
         <x:v>ファシリテーション</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="H1" s="3" t="str">
         <x:v>所属グループ</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="I1" s="3" t="str">
         <x:v>備考</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="15" t="str">
+      <x:c r="A2" s="7" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B2" s="15" t="str">
+      <x:c r="B2" s="7" t="str">
+        <x:v>ignore</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="C2" s="15" t="str">
+      <x:c r="D2" s="7" t="str">
         <x:v>ordinal</x:v>
       </x:c>
-      <x:c r="D2" s="15" t="str">
+      <x:c r="E2" s="7" t="str">
         <x:v>ordinal</x:v>
       </x:c>
-      <x:c r="E2" s="15" t="str">
+      <x:c r="F2" s="7" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="F2" s="15" t="str">
+      <x:c r="G2" s="7" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="G2" s="15" t="str">
+      <x:c r="H2" s="7" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="H2" s="15" t="str">
+      <x:c r="I2" s="7" t="str">
         <x:v>ignore</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" t="str">
         <x:v>メンバー01</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
+      <x:c r="B3" t="str">
+        <x:v>メンバー 01</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
         <x:v>データ</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="n">
+      <x:c r="D3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="n">
+      <x:c r="E3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="16" t="str">
+      <x:c r="F3" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="str">
+      <x:c r="G3" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="G3" s="16" t="str">
+      <x:c r="H3" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H3" s="16" t="str"/>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" t="str">
         <x:v>メンバー02</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" t="str">
+        <x:v>メンバー 02</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
         <x:v>デザイン</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="n">
+      <x:c r="D4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="n">
+      <x:c r="E4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="str">
+      <x:c r="F4" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H4" s="16" t="str"/>
+      <x:c r="I4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" t="str">
         <x:v>メンバー03</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" t="str">
+        <x:v>メンバー 03</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
         <x:v>営業</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="n">
+      <x:c r="D5" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="n">
+      <x:c r="E5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
+      <x:c r="F5" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H5" s="16" t="str"/>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" t="str">
         <x:v>メンバー04</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B6" t="str">
+        <x:v>メンバー 04</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
         <x:v>企画</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="n">
+      <x:c r="D6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="n">
+      <x:c r="E6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="str">
+      <x:c r="F6" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="str"/>
+      <x:c r="I6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" t="str">
         <x:v>メンバー05</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" t="str">
+        <x:v>メンバー 05</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
         <x:v>開発</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="n">
+      <x:c r="D7" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="n">
+      <x:c r="E7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="str">
+      <x:c r="F7" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="str">
+      <x:c r="G7" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H7" s="16" t="str"/>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="16" t="str">
+      <x:c r="A8" t="str">
         <x:v>メンバー06</x:v>
       </x:c>
-      <x:c r="B8" s="16" t="str">
+      <x:c r="B8" t="str">
+        <x:v>メンバー 06</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
         <x:v>運営</x:v>
       </x:c>
-      <x:c r="C8" s="16" t="n">
+      <x:c r="D8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="n">
+      <x:c r="E8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E8" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F8" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G8" s="16" t="str">
+      <x:c r="F8" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H8" s="16" t="str"/>
+      <x:c r="I8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="A9" t="str">
         <x:v>メンバー07</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" t="str">
+        <x:v>メンバー 07</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
         <x:v>データ</x:v>
       </x:c>
-      <x:c r="C9" s="16" t="n">
+      <x:c r="D9" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="n">
+      <x:c r="E9" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E9" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F9" s="16" t="str">
+      <x:c r="F9" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="G9" s="16" t="str">
+      <x:c r="H9" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str"/>
+      <x:c r="I9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="16" t="str">
+      <x:c r="A10" t="str">
         <x:v>メンバー08</x:v>
       </x:c>
-      <x:c r="B10" s="16" t="str">
+      <x:c r="B10" t="str">
+        <x:v>メンバー 08</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
         <x:v>デザイン</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="n">
+      <x:c r="D10" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="n">
+      <x:c r="E10" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="str">
+      <x:c r="F10" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="str"/>
+      <x:c r="I10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="16" t="str">
+      <x:c r="A11" t="str">
         <x:v>メンバー09</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B11" t="str">
+        <x:v>メンバー 09</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
         <x:v>営業</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="n">
+      <x:c r="D11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="n">
+      <x:c r="E11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="str">
+      <x:c r="F11" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="str">
+      <x:c r="G11" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H11" s="16" t="str"/>
+      <x:c r="I11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="16" t="str">
+      <x:c r="A12" t="str">
         <x:v>メンバー10</x:v>
       </x:c>
-      <x:c r="B12" s="16" t="str">
+      <x:c r="B12" t="str">
+        <x:v>メンバー 10</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
         <x:v>企画</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="n">
+      <x:c r="D12" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="n">
+      <x:c r="E12" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="str">
+      <x:c r="F12" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="str"/>
+      <x:c r="I12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="16" t="str">
+      <x:c r="A13" t="str">
         <x:v>メンバー11</x:v>
       </x:c>
-      <x:c r="B13" s="16" t="str">
+      <x:c r="B13" t="str">
+        <x:v>メンバー 11</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
         <x:v>開発</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="n">
+      <x:c r="D13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="n">
+      <x:c r="E13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="str">
+      <x:c r="F13" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str"/>
+      <x:c r="I13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="16" t="str">
+      <x:c r="A14" t="str">
         <x:v>メンバー12</x:v>
       </x:c>
-      <x:c r="B14" s="16" t="str">
+      <x:c r="B14" t="str">
+        <x:v>メンバー 12</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
         <x:v>運営</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="n">
+      <x:c r="D14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="n">
+      <x:c r="E14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="str">
+      <x:c r="F14" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H14" s="16" t="str"/>
+      <x:c r="I14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="16" t="str">
+      <x:c r="A15" t="str">
         <x:v>メンバー13</x:v>
       </x:c>
-      <x:c r="B15" s="16" t="str">
+      <x:c r="B15" t="str">
+        <x:v>メンバー 13</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
         <x:v>データ</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="n">
+      <x:c r="D15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="n">
+      <x:c r="E15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="str">
+      <x:c r="F15" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F15" s="16" t="str">
+      <x:c r="G15" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="G15" s="16" t="str">
+      <x:c r="H15" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H15" s="16" t="str"/>
+      <x:c r="I15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="16" t="str">
+      <x:c r="A16" t="str">
         <x:v>メンバー14</x:v>
       </x:c>
-      <x:c r="B16" s="16" t="str">
+      <x:c r="B16" t="str">
+        <x:v>メンバー 14</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
         <x:v>デザイン</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="n">
+      <x:c r="D16" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="n">
+      <x:c r="E16" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="str">
+      <x:c r="F16" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="str"/>
+      <x:c r="I16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="16" t="str">
+      <x:c r="A17" t="str">
         <x:v>メンバー15</x:v>
       </x:c>
-      <x:c r="B17" s="16" t="str">
+      <x:c r="B17" t="str">
+        <x:v>メンバー 15</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
         <x:v>営業</x:v>
       </x:c>
-      <x:c r="C17" s="16" t="n">
+      <x:c r="D17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="n">
+      <x:c r="E17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="str">
+      <x:c r="F17" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="str"/>
+      <x:c r="I17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="16" t="str">
+      <x:c r="A18" t="str">
         <x:v>メンバー16</x:v>
       </x:c>
-      <x:c r="B18" s="16" t="str">
+      <x:c r="B18" t="str">
+        <x:v>メンバー 16</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
         <x:v>企画</x:v>
       </x:c>
-      <x:c r="C18" s="16" t="n">
+      <x:c r="D18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="n">
+      <x:c r="E18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="str">
+      <x:c r="F18" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="str"/>
+      <x:c r="I18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="16" t="str">
+      <x:c r="A19" t="str">
         <x:v>メンバー17</x:v>
       </x:c>
-      <x:c r="B19" s="16" t="str">
+      <x:c r="B19" t="str">
+        <x:v>メンバー 17</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
         <x:v>開発</x:v>
       </x:c>
-      <x:c r="C19" s="16" t="n">
+      <x:c r="D19" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="n">
+      <x:c r="E19" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E19" s="16" t="str">
+      <x:c r="F19" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F19" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="str">
+      <x:c r="G19" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H19" s="16" t="str"/>
+      <x:c r="I19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="16" t="str">
+      <x:c r="A20" t="str">
         <x:v>メンバー18</x:v>
       </x:c>
-      <x:c r="B20" s="16" t="str">
+      <x:c r="B20" t="str">
+        <x:v>メンバー 18</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
         <x:v>運営</x:v>
       </x:c>
-      <x:c r="C20" s="16" t="n">
+      <x:c r="D20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="n">
+      <x:c r="E20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E20" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="str">
+      <x:c r="F20" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H20" s="16" t="str"/>
+      <x:c r="I20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="16" t="str">
+      <x:c r="A21" t="str">
         <x:v>メンバー19</x:v>
       </x:c>
-      <x:c r="B21" s="16" t="str">
+      <x:c r="B21" t="str">
+        <x:v>メンバー 19</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
         <x:v>データ</x:v>
       </x:c>
-      <x:c r="C21" s="16" t="n">
+      <x:c r="D21" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="n">
+      <x:c r="E21" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E21" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="str">
+      <x:c r="F21" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="G21" s="16" t="str">
+      <x:c r="H21" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H21" s="16" t="str"/>
+      <x:c r="I21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="16" t="str">
+      <x:c r="A22" t="str">
         <x:v>メンバー20</x:v>
       </x:c>
-      <x:c r="B22" s="16" t="str">
+      <x:c r="B22" t="str">
+        <x:v>メンバー 20</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
         <x:v>デザイン</x:v>
       </x:c>
-      <x:c r="C22" s="16" t="n">
+      <x:c r="D22" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="n">
+      <x:c r="E22" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E22" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="str">
+      <x:c r="F22" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H22" s="16" t="str"/>
+      <x:c r="I22"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="16" t="str">
+      <x:c r="A23" t="str">
         <x:v>メンバー21</x:v>
       </x:c>
-      <x:c r="B23" s="16" t="str">
+      <x:c r="B23" t="str">
+        <x:v>メンバー 21</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
         <x:v>営業</x:v>
       </x:c>
-      <x:c r="C23" s="16" t="n">
+      <x:c r="D23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="n">
+      <x:c r="E23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E23" s="16" t="str">
+      <x:c r="F23" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F23" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="str">
+      <x:c r="G23" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H23" s="16" t="str"/>
+      <x:c r="I23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="16" t="str">
+      <x:c r="A24" t="str">
         <x:v>メンバー22</x:v>
       </x:c>
-      <x:c r="B24" s="16" t="str">
+      <x:c r="B24" t="str">
+        <x:v>メンバー 22</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
         <x:v>企画</x:v>
       </x:c>
-      <x:c r="C24" s="16" t="n">
+      <x:c r="D24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="n">
+      <x:c r="E24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E24" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="str">
+      <x:c r="F24" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="str"/>
+      <x:c r="I24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="16" t="str">
+      <x:c r="A25" t="str">
         <x:v>メンバー23</x:v>
       </x:c>
-      <x:c r="B25" s="16" t="str">
+      <x:c r="B25" t="str">
+        <x:v>メンバー 23</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
         <x:v>開発</x:v>
       </x:c>
-      <x:c r="C25" s="16" t="n">
+      <x:c r="D25" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="n">
+      <x:c r="E25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E25" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F25" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="str">
+      <x:c r="F25" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H25" s="16" t="str"/>
+      <x:c r="I25"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="16" t="str">
+      <x:c r="A26" t="str">
         <x:v>メンバー24</x:v>
       </x:c>
-      <x:c r="B26" s="16" t="str">
+      <x:c r="B26" t="str">
+        <x:v>メンバー 24</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
         <x:v>運営</x:v>
       </x:c>
-      <x:c r="C26" s="16" t="n">
+      <x:c r="D26" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="n">
+      <x:c r="E26" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E26" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="str">
+      <x:c r="F26" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H26" s="16" t="str"/>
+      <x:c r="I26"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="16" t="str">
+      <x:c r="A27" t="str">
         <x:v>メンバー25</x:v>
       </x:c>
-      <x:c r="B27" s="16" t="str">
+      <x:c r="B27" t="str">
+        <x:v>メンバー 25</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
         <x:v>データ</x:v>
       </x:c>
-      <x:c r="C27" s="16" t="n">
+      <x:c r="D27" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="n">
+      <x:c r="E27" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E27" s="16" t="str">
+      <x:c r="F27" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F27" s="16" t="str">
+      <x:c r="G27" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="G27" s="16" t="str">
+      <x:c r="H27" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H27" s="16" t="str"/>
+      <x:c r="I27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="16" t="str">
+      <x:c r="A28" t="str">
         <x:v>メンバー26</x:v>
       </x:c>
-      <x:c r="B28" s="16" t="str">
+      <x:c r="B28" t="str">
+        <x:v>メンバー 26</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
         <x:v>デザイン</x:v>
       </x:c>
-      <x:c r="C28" s="16" t="n">
+      <x:c r="D28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="n">
+      <x:c r="E28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E28" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F28" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G28" s="16" t="str">
+      <x:c r="F28" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H28" s="16" t="str"/>
+      <x:c r="I28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="16" t="str">
+      <x:c r="A29" t="str">
         <x:v>メンバー27</x:v>
       </x:c>
-      <x:c r="B29" s="16" t="str">
+      <x:c r="B29" t="str">
+        <x:v>メンバー 27</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
         <x:v>営業</x:v>
       </x:c>
-      <x:c r="C29" s="16" t="n">
+      <x:c r="D29" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="n">
+      <x:c r="E29" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E29" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F29" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G29" s="16" t="str">
+      <x:c r="F29" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H29" s="16" t="str"/>
+      <x:c r="I29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="16" t="str">
+      <x:c r="A30" t="str">
         <x:v>メンバー28</x:v>
       </x:c>
-      <x:c r="B30" s="16" t="str">
+      <x:c r="B30" t="str">
+        <x:v>メンバー 28</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
         <x:v>企画</x:v>
       </x:c>
-      <x:c r="C30" s="16" t="n">
+      <x:c r="D30" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="n">
+      <x:c r="E30" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E30" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F30" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="str">
+      <x:c r="F30" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="H30" s="16" t="str"/>
+      <x:c r="I30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="16" t="str">
+      <x:c r="A31" t="str">
         <x:v>メンバー29</x:v>
       </x:c>
-      <x:c r="B31" s="16" t="str">
+      <x:c r="B31" t="str">
+        <x:v>メンバー 29</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
         <x:v>開発</x:v>
       </x:c>
-      <x:c r="C31" s="16" t="n">
+      <x:c r="D31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D31" s="16" t="n">
+      <x:c r="E31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E31" s="16" t="str">
+      <x:c r="F31" t="str">
         <x:v>はい</x:v>
       </x:c>
-      <x:c r="F31" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G31" s="16" t="str">
+      <x:c r="G31" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H31" s="16" t="str"/>
+      <x:c r="I31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="16" t="str">
+      <x:c r="A32" t="str">
         <x:v>メンバー30</x:v>
       </x:c>
-      <x:c r="B32" s="16" t="str">
+      <x:c r="B32" t="str">
+        <x:v>メンバー 30</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
         <x:v>運営</x:v>
       </x:c>
-      <x:c r="C32" s="16" t="n">
+      <x:c r="D32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D32" s="16" t="n">
+      <x:c r="E32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E32" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="str">
-        <x:v>いいえ</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="str">
+      <x:c r="F32" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>いいえ</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="H32" s="16" t="str"/>
+      <x:c r="I32"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="C3:C32">
-    <x:cfRule type="dataBar" priority="1">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFA02B93"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0F74217F-E0C6-2491-DF98-71CA771E7391}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D3:D32">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFA02B93"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9BBCFD70-C6A7-480D-340F-9E32EF11DD25}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting>
-          <x14:cfRule type="dataBar" priority="1" id="{0F74217F-E0C6-2491-DF98-71CA771E7391}">
-            <x14:dataBar gradient="1">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:fillColor rgb="FFA02B93"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>C3:C32</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting>
-          <x14:cfRule type="dataBar" priority="2" id="{9BBCFD70-C6A7-480D-340F-9E32EF11DD25}">
-            <x14:dataBar gradient="1">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:fillColor rgb="FFA02B93"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D3:D32</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </x:ext>
-  </x:extLst>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="26" t="str">
-        <x:v>汎用 — プロジェクト・ワークショップ編成（30人）</x:v>
-      </x:c>
-      <x:c r="B1" s="26" t="str"/>
-      <x:c r="C1" s="26" t="str"/>
-      <x:c r="D1" s="26" t="str"/>
+      <x:c r="A1" s="10" t="str">
+        <x:v>Group Builder 日本語テンプレート</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str"/>
+      <x:c r="C1" s="10" t="str"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="27" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>項目</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>型</x:v>
       </x:c>
-      <x:c r="B2" s="27" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="C2" s="27" t="str">
-        <x:v>例</x:v>
-      </x:c>
-      <x:c r="D2" s="27" t="str">
-        <x:v>Group Builderでの扱い</x:v>
+      <x:c r="C2" s="7" t="str">
+        <x:v>用途</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
-        <x:v>識別子</x:v>
-      </x:c>
-      <x:c r="C3" s="16" t="str">
-        <x:v>氏名・メンバー名</x:v>
-      </x:c>
-      <x:c r="D3" s="16" t="str">
-        <x:v>最適化しない</x:v>
+      <x:c r="C3" t="str">
+        <x:v>メンバー識別</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" t="str">
+        <x:v>フリガナ</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>ignore</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Pair Rules の検索・あいうえお順に使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
-        <x:v>カテゴリ</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="str">
-        <x:v>部署・専門分野・ポジション</x:v>
-      </x:c>
-      <x:c r="D4" s="16" t="str">
-        <x:v>カテゴリ比率を分散</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="B5" t="str">
+        <x:v>category</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>カテゴリ属性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
         <x:v>numeric</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B6" t="str">
+        <x:v>numeric</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
         <x:v>連続数値</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>売上・年齢・スコア</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>グループ平均を揃える</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="16" t="str">
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
         <x:v>ordinal</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B7" t="str">
+        <x:v>ordinal</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
         <x:v>順序尺度</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
-        <x:v>経験1〜5・リーダー1〜5</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="str">
-        <x:v>各段階の分布を揃える</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="16" t="str">
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
-        <x:v>Yes/No</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="str">
-        <x:v>資格あり・要配慮</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="str">
-        <x:v>該当人数を分散</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="16" t="str">
+      <x:c r="B8" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>はい / いいえ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
         <x:v>ignore</x:v>
       </x:c>
-      <x:c r="B8" s="16" t="str">
-        <x:v>参考情報</x:v>
-      </x:c>
-      <x:c r="C8" s="16" t="str">
-        <x:v>備考・連絡先</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="str">
-        <x:v>最適化しない</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="16" t="str"/>
-      <x:c r="B9" s="16" t="str"/>
-      <x:c r="C9" s="16" t="str"/>
-      <x:c r="D9" s="16" t="str"/>
+      <x:c r="B9" t="str">
+        <x:v>ignore</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>最適化には使用しない</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="16" t="str">
-        <x:v>用途</x:v>
-      </x:c>
-      <x:c r="B10" s="16" t="str">
-        <x:v>社内外の研修、ハッカソン、ワークショップ、プロジェクトチーム</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="str"/>
-      <x:c r="D10" s="16" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="16" t="str">
-        <x:v>ポイント</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:v>専門・経験・コミュニケーション能力をバランスよく分散する</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str"/>
-      <x:c r="D11" s="16" t="str"/>
+      <x:c r="A10" t="str">
+        <x:v>Pair Rules</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>フリガナ列を自動検出</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>フリガナがない場合は名前順にフォールバック</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A1:C1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
